--- a/output/pdf_financials_xlsx/FV.H.xlsx
+++ b/output/pdf_financials_xlsx/FV.H.xlsx
@@ -19362,10 +19362,10 @@
         </is>
       </c>
       <c r="Q107" s="5" t="n">
-        <v>0.148025</v>
+        <v>-0.148025</v>
       </c>
       <c r="R107" s="5" t="n">
-        <v>0.123526</v>
+        <v>-0.123526</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FV.H.xlsx
+++ b/output/pdf_financials_xlsx/FV.H.xlsx
@@ -1159,15 +1159,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>0.106661</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.0356</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -1179,10 +1175,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="3" t="n">
+        <v>0.002832</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -2789,22 +2783,22 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003772</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.010281</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.6243300000000001</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.561389</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.458089</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.376975</v>
       </c>
     </row>
     <row r="35">
@@ -2917,22 +2911,22 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003772</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.010281</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.6243300000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.561389</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.458089</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.376975</v>
       </c>
     </row>
     <row r="37">
@@ -9807,7 +9801,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -23951,7 +23945,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -24774,7 +24768,11 @@
           <t>General and administrative (note</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -26960,7 +26958,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -28517,7 +28515,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
